--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.17530605075127</v>
+        <v>11.89098723324708</v>
       </c>
       <c r="D2" t="n">
-        <v>51.3419493761017</v>
+        <v>8.343066773616528</v>
       </c>
       <c r="E2" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F2" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.13823694218021</v>
+        <v>10.58496350310429</v>
       </c>
       <c r="D3" t="n">
-        <v>42.24230619183636</v>
+        <v>6.864374756173409</v>
       </c>
       <c r="E3" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F3" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.0222644772447</v>
+        <v>3.091117977552265</v>
       </c>
       <c r="D4" t="n">
-        <v>17.54154976492849</v>
+        <v>2.850501836800879</v>
       </c>
       <c r="E4" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F4" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.14878796695726</v>
+        <v>2.136678044630555</v>
       </c>
       <c r="D5" t="n">
-        <v>5.81365658871148</v>
+        <v>0.9447191956656155</v>
       </c>
       <c r="E5" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F5" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.97107661536344</v>
+        <v>5.19529994999656</v>
       </c>
       <c r="D6" t="n">
-        <v>32.34424885967622</v>
+        <v>5.255940439697386</v>
       </c>
       <c r="E6" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F6" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.22646423324687</v>
+        <v>4.586800437902617</v>
       </c>
       <c r="D7" t="n">
-        <v>17.71871042550321</v>
+        <v>2.879290444144273</v>
       </c>
       <c r="E7" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F7" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.9463123325993</v>
+        <v>3.566275754047386</v>
       </c>
       <c r="D8" t="n">
-        <v>14.25403431844339</v>
+        <v>2.31628057674705</v>
       </c>
       <c r="E8" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F8" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.22224099066826</v>
+        <v>4.748614160983593</v>
       </c>
       <c r="D9" t="n">
-        <v>23.77381160949093</v>
+        <v>3.863244386542276</v>
       </c>
       <c r="E9" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F9" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.08378769509731</v>
+        <v>7.488615500453313</v>
       </c>
       <c r="D10" t="n">
-        <v>11.54780612689053</v>
+        <v>1.876518495619712</v>
       </c>
       <c r="E10" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F10" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>70.52150490429266</v>
+        <v>11.45974454694756</v>
       </c>
       <c r="D11" t="n">
-        <v>32.49954635395604</v>
+        <v>5.281176282517857</v>
       </c>
       <c r="E11" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F11" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.66965055720876</v>
+        <v>7.421318215546424</v>
       </c>
       <c r="D12" t="n">
-        <v>45.06153168073018</v>
+        <v>7.322498898118655</v>
       </c>
       <c r="E12" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F12" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>50.12434551220797</v>
+        <v>8.145206145733797</v>
       </c>
       <c r="D13" t="n">
-        <v>50.58435738528332</v>
+        <v>8.21995807510854</v>
       </c>
       <c r="E13" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F13" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>49.40196558527177</v>
+        <v>8.027819407606662</v>
       </c>
       <c r="D14" t="n">
-        <v>49.10271485851356</v>
+        <v>7.979191164508453</v>
       </c>
       <c r="E14" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F14" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>50.78811398955347</v>
+        <v>8.253068523302439</v>
       </c>
       <c r="D15" t="n">
-        <v>51.06166052092637</v>
+        <v>8.297519834650535</v>
       </c>
       <c r="E15" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F15" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>52.08948245272141</v>
+        <v>8.464540898567229</v>
       </c>
       <c r="D16" t="n">
-        <v>52.0508946474343</v>
+        <v>8.458270380208075</v>
       </c>
       <c r="E16" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F16" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>52.36767349515912</v>
+        <v>8.509746942963359</v>
       </c>
       <c r="D17" t="n">
-        <v>52.53161850187243</v>
+        <v>8.536388006554271</v>
       </c>
       <c r="E17" t="n">
-        <v>17.55183852899815</v>
+        <v>2.852173760962199</v>
       </c>
       <c r="F17" t="n">
-        <v>16.3681430758421</v>
+        <v>2.659823249824341</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
